--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_calcium/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_calcium.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_calcium/10.3334_CDIAC_SPRUCE.005/10.3334_CDIAC_SPRUCE.005_soil_Major_and_trace_elements_total__Total_calcium.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="47" customWidth="1" min="7" max="7"/>
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -579,12 +579,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -744,12 +744,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1404,12 +1404,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1789,12 +1789,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1899,12 +1899,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2009,12 +2009,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2174,12 +2174,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2284,12 +2284,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2614,12 +2614,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2724,12 +2724,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2927,7 +2927,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2944,12 +2944,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3109,12 +3109,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3164,12 +3164,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3312,7 +3312,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3329,12 +3329,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3384,12 +3384,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3439,12 +3439,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3494,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3549,12 +3549,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3604,12 +3604,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3769,12 +3769,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3989,12 +3989,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -4027,7 +4027,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4044,12 +4044,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4099,12 +4099,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4154,12 +4154,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4209,12 +4209,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4319,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4429,12 +4429,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4649,12 +4649,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4704,12 +4704,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4759,12 +4759,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4814,12 +4814,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4869,12 +4869,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4924,12 +4924,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4979,12 +4979,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5144,12 +5144,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5199,12 +5199,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5402,7 +5402,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5419,12 +5419,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5474,12 +5474,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5677,7 +5677,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5694,12 +5694,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5914,12 +5914,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6024,12 +6024,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6244,12 +6244,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6354,12 +6354,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6392,7 +6392,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6409,12 +6409,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6464,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6519,12 +6519,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6629,12 +6629,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6739,12 +6739,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6904,12 +6904,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6959,12 +6959,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7014,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7069,12 +7069,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7179,12 +7179,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -7217,7 +7217,7 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -7382,7 +7382,7 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7399,12 +7399,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7509,12 +7509,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7619,12 +7619,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7674,12 +7674,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7729,12 +7729,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7949,12 +7949,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8004,12 +8004,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8114,12 +8114,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8224,12 +8224,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8279,12 +8279,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8334,12 +8334,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8389,12 +8389,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8444,12 +8444,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8499,12 +8499,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8554,12 +8554,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8592,7 +8592,7 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8664,12 +8664,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8702,7 +8702,7 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8719,12 +8719,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8774,12 +8774,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8829,12 +8829,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8884,12 +8884,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8939,12 +8939,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8977,7 +8977,7 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8994,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9104,12 +9104,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9159,12 +9159,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9214,12 +9214,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -9252,7 +9252,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9269,12 +9269,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -9307,7 +9307,7 @@
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9379,12 +9379,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9434,12 +9434,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="M165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9599,12 +9599,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9709,12 +9709,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9764,12 +9764,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="M170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9857,7 +9857,7 @@
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9874,12 +9874,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9984,12 +9984,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10094,12 +10094,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="M176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10149,12 +10149,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="M178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10259,12 +10259,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="M179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10314,12 +10314,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="M180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10369,12 +10369,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10424,12 +10424,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10479,12 +10479,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10534,12 +10534,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10644,12 +10644,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="M187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10754,12 +10754,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10864,12 +10864,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10919,12 +10919,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10957,7 +10957,7 @@
       </c>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -11012,7 +11012,7 @@
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11029,12 +11029,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -11067,7 +11067,7 @@
       </c>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -11122,7 +11122,7 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11139,12 +11139,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -11177,7 +11177,7 @@
       </c>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11194,12 +11194,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11249,12 +11249,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11304,12 +11304,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11359,12 +11359,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11414,12 +11414,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11469,12 +11469,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11524,12 +11524,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -11562,7 +11562,7 @@
       </c>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11579,12 +11579,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11634,12 +11634,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11672,7 +11672,7 @@
       </c>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11689,12 +11689,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11744,12 +11744,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="M206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11799,12 +11799,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="M207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11854,12 +11854,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11892,7 +11892,7 @@
       </c>
       <c r="M208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11909,12 +11909,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="M209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11964,12 +11964,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -12002,7 +12002,7 @@
       </c>
       <c r="M210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12019,12 +12019,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12129,12 +12129,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="M213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="M214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12239,12 +12239,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12294,12 +12294,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -12332,7 +12332,7 @@
       </c>
       <c r="M216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12349,12 +12349,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -12387,7 +12387,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12404,12 +12404,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="M218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12459,12 +12459,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="M219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12514,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="M220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12569,12 +12569,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="M221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12624,12 +12624,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -12662,7 +12662,7 @@
       </c>
       <c r="M222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12679,12 +12679,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="M223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12734,12 +12734,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12772,7 +12772,7 @@
       </c>
       <c r="M224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12789,12 +12789,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="M225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12844,12 +12844,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="M226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12899,12 +12899,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="M227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12954,12 +12954,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="M228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13009,12 +13009,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="M229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13064,12 +13064,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="M230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13119,12 +13119,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -13157,7 +13157,7 @@
       </c>
       <c r="M231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="M232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13229,12 +13229,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="M233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13284,12 +13284,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -13322,7 +13322,7 @@
       </c>
       <c r="M234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13339,12 +13339,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="M235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13394,12 +13394,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -13432,7 +13432,7 @@
       </c>
       <c r="M236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13449,12 +13449,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="M237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13504,12 +13504,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="M238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="M239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13614,12 +13614,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="M240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13669,12 +13669,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13724,12 +13724,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="M242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13779,12 +13779,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13834,12 +13834,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13872,7 +13872,7 @@
       </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13889,12 +13889,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13927,7 +13927,7 @@
       </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13944,12 +13944,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13999,12 +13999,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14054,12 +14054,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -14092,7 +14092,7 @@
       </c>
       <c r="M248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14109,12 +14109,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="M249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14164,12 +14164,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -14202,7 +14202,7 @@
       </c>
       <c r="M250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14219,12 +14219,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="M251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14274,12 +14274,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="M252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="M253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="M254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14439,12 +14439,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="M255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14494,12 +14494,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="M256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14549,12 +14549,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14604,12 +14604,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -14642,7 +14642,7 @@
       </c>
       <c r="M258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14659,12 +14659,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="M259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14714,12 +14714,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="M260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14769,12 +14769,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="M261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14824,12 +14824,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="M262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14879,12 +14879,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       </c>
       <c r="M263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14934,12 +14934,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14972,7 +14972,7 @@
       </c>
       <c r="M264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14989,12 +14989,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="M265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15044,12 +15044,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -15082,7 +15082,7 @@
       </c>
       <c r="M266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15099,12 +15099,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="M267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15154,12 +15154,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -15192,7 +15192,7 @@
       </c>
       <c r="M268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15209,12 +15209,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -15247,7 +15247,7 @@
       </c>
       <c r="M269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15264,12 +15264,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -15302,7 +15302,7 @@
       </c>
       <c r="M270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15319,12 +15319,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="M271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15374,12 +15374,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="M272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15429,12 +15429,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="M273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15484,12 +15484,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15539,12 +15539,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -15577,7 +15577,7 @@
       </c>
       <c r="M275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15594,12 +15594,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="M276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15649,12 +15649,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15704,12 +15704,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15759,12 +15759,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -15797,7 +15797,7 @@
       </c>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15814,12 +15814,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15869,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15907,7 +15907,7 @@
       </c>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15924,12 +15924,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15962,7 +15962,7 @@
       </c>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15979,12 +15979,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -16017,7 +16017,7 @@
       </c>
       <c r="M283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16034,12 +16034,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -16072,7 +16072,7 @@
       </c>
       <c r="M284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16089,12 +16089,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="M285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16144,12 +16144,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="M286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16199,12 +16199,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="M287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16254,12 +16254,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="M288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16309,12 +16309,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="M289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16364,12 +16364,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="M290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16419,12 +16419,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -16457,7 +16457,7 @@
       </c>
       <c r="M291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16474,12 +16474,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -16512,7 +16512,7 @@
       </c>
       <c r="M292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16529,12 +16529,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="M293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16584,12 +16584,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="M294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16639,12 +16639,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="M295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -16694,12 +16694,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -16732,7 +16732,7 @@
       </c>
       <c r="M296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Ca (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
